--- a/sample_tasks.xlsx
+++ b/sample_tasks.xlsx
@@ -348,7 +348,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>0.0005612805154588951</v>
+        <v>89879.09120448407</v>
       </c>
     </row>
     <row r="3">
